--- a/CodeSystem-pcor-item-dictionary.xlsx
+++ b/CodeSystem-pcor-item-dictionary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -793,6 +793,84 @@
     <t>AN_subtyp — Welchem Subtyp der Anorexia nervosa würden Sie sich zu ordnen?</t>
   </si>
   <si>
+    <t>AN_biography</t>
+  </si>
+  <si>
+    <t>AN_biography — Wie lange sind Sie bereits von Ihrer Essstörung betroffen?</t>
+  </si>
+  <si>
+    <t>lowBMI</t>
+  </si>
+  <si>
+    <t>lowBMI — Welches war Ihr niedrigter BMI?</t>
+  </si>
+  <si>
+    <t>treatment_outpatient</t>
+  </si>
+  <si>
+    <t>treatment_outpatient — Sind Sie zurzeit in psychotherapeutischer Behandlung?</t>
+  </si>
+  <si>
+    <t>traumaspecific1</t>
+  </si>
+  <si>
+    <t>traumaspecific1 — Handelt es sich bei Ihrer Angabe um ein einmaliges oder um ein sich …</t>
+  </si>
+  <si>
+    <t>traumaspecific2</t>
+  </si>
+  <si>
+    <t>traumaspecific2 — Passierte dieses Ereignis vor oder nach den ersten Anzeichen der …</t>
+  </si>
+  <si>
+    <t>traumaspecific3</t>
+  </si>
+  <si>
+    <t>traumaspecific3 — Handelt es sich bei Ihrer Angabe um ein einmaliges oder um ein sich …</t>
+  </si>
+  <si>
+    <t>traumaspecific4</t>
+  </si>
+  <si>
+    <t>traumaspecific4 — Passierte dieses Ereignis vor oder nach den ersten Anzeichen der …</t>
+  </si>
+  <si>
+    <t>traumaspecific5</t>
+  </si>
+  <si>
+    <t>traumaspecific5 — Handelt es sich bei Ihrer Angabe um ein einmaliges oder um ein sich …</t>
+  </si>
+  <si>
+    <t>traumaspecific6</t>
+  </si>
+  <si>
+    <t>traumaspecific6 — Passierte dieses Ereignis vor oder nach den ersten Anzeichen der …</t>
+  </si>
+  <si>
+    <t>life_event1_screening</t>
+  </si>
+  <si>
+    <t>life_event1_screening — Gab es in Ihrem Leben prägende belastende Lebensereignisse, die Sie …</t>
+  </si>
+  <si>
+    <t>life_event1_monitoring</t>
+  </si>
+  <si>
+    <t>life_event1_monitoring — Gab es seit der letzten Befragung prägende belastende …</t>
+  </si>
+  <si>
+    <t>lifev_discharge</t>
+  </si>
+  <si>
+    <t>lifev_discharge — Gab es seit Ihrer Aufnahme prägende belastende Lebensereignisse, …</t>
+  </si>
+  <si>
+    <t>lifev_text</t>
+  </si>
+  <si>
+    <t>lifev_text — Bitte benennen Sie diese Lebensereignisse:</t>
+  </si>
+  <si>
     <t>medication1</t>
   </si>
   <si>
@@ -805,6 +883,36 @@
     <t>medication_text — Bitte nennen Sie alle Medikamente, die sie aktuell regelmäßig oder …</t>
   </si>
   <si>
+    <t>new_diagnosis_monitoring</t>
+  </si>
+  <si>
+    <t>new_diagnosis_monitoring — Gab es seit der letzten Befragung weitere medizinische / psychische …</t>
+  </si>
+  <si>
+    <t>new_diagnosis_discharge</t>
+  </si>
+  <si>
+    <t>new_diagnosis_discharge — Gab es seit Ihrer Aufnahme weitere medizinische / psychische …</t>
+  </si>
+  <si>
+    <t>new_diagnosis_text</t>
+  </si>
+  <si>
+    <t>new_diagnosis_text — Bitte tragen Sie diese Diagnosen in das folgende Textfeld ein.</t>
+  </si>
+  <si>
+    <t>bdkm15</t>
+  </si>
+  <si>
+    <t>bdkm15 — Waren Sie früher oder sind Sie zurzeit in psychotherapeutischer …</t>
+  </si>
+  <si>
+    <t>bdkm16</t>
+  </si>
+  <si>
+    <t>bdkm16 — Wie oft haben Sie in den letzten 4 Wochen einen Arzt aufgesucht?</t>
+  </si>
+  <si>
     <t>weight_outpatient_1</t>
   </si>
   <si>
@@ -827,6 +935,18 @@
   </si>
   <si>
     <t>weight_discharge — Wie viel wiegen Sie aktuell in kg?</t>
+  </si>
+  <si>
+    <t>diagnosis_admit</t>
+  </si>
+  <si>
+    <t>diagnosis_admit — Welche Diagnose/-n sollen bei Ihnen hier behandelt werden?</t>
+  </si>
+  <si>
+    <t>comorbid1</t>
+  </si>
+  <si>
+    <t>comorbid1 — Gibt es außer den zurvor genannten Diagnosen noch andere Diagnosen?</t>
   </si>
   <si>
     <t>WAI01</t>
@@ -1218,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2603,6 +2723,246 @@
       </c>
       <c r="D115" s="2"/>
     </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="D118" s="2"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="D119" s="2"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="D120" s="2"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="D121" s="2"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="D125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="D133" s="2"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="D135" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-pcor-item-dictionary.xlsx
+++ b/CodeSystem-pcor-item-dictionary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="339">
   <si>
     <t>Property</t>
   </si>
@@ -845,6 +845,72 @@
   </si>
   <si>
     <t>traumaspecific6 — Passierte dieses Ereignis vor oder nach den ersten Anzeichen der …</t>
+  </si>
+  <si>
+    <t>edp1</t>
+  </si>
+  <si>
+    <t>edp1 — Angst vor Gewichtszunahme (Schlankheitsstreben) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp2</t>
+  </si>
+  <si>
+    <t>edp2 — Essmenge vor anderen, Essanfaelle allein (Bulimie) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp3</t>
+  </si>
+  <si>
+    <t>edp3 — Unzufriedenheit mit Koerperstellen (Koerperunzufriedenheit) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp4</t>
+  </si>
+  <si>
+    <t>edp4 — geringe Selbstbewertung (Ineffektivitaet) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp5</t>
+  </si>
+  <si>
+    <t>edp5 — Anspruch, der/die Beste zu sein (Perfektionismus) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp6</t>
+  </si>
+  <si>
+    <t>edp6 — Naehe in Beziehungen (Misstrauen, invers) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp7</t>
+  </si>
+  <si>
+    <t>edp7 — Gefuehle benennen koennen (interozeptive Wahrnehmung) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp8</t>
+  </si>
+  <si>
+    <t>edp8 — Haltung zum Erwachsensein (Angst vor dem Erwachsenwerden, invers) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp9</t>
+  </si>
+  <si>
+    <t>edp9 — Genuss beim Essen als Schwaeche (Askese) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp10</t>
+  </si>
+  <si>
+    <t>edp10 — spontane Aeusserungen, die bereut werden (Impulsregulation) [metadata-only: Originalwortlaut nicht abgebildet]</t>
+  </si>
+  <si>
+    <t>edp11</t>
+  </si>
+  <si>
+    <t>edp11 — Kontaktfreude (soziale Unsicherheit, invers) [metadata-only: Originalwortlaut nicht abgebildet]</t>
   </si>
   <si>
     <t>life_event1_screening</t>
@@ -1338,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +3029,138 @@
       </c>
       <c r="D135" s="2"/>
     </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="D136" s="2"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="D137" s="2"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="D139" s="2"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="D144" s="2"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="D145" s="2"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="D146" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
